--- a/artfynd/A 44466-2023 artfynd.xlsx
+++ b/artfynd/A 44466-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44466-2023 artfynd.xlsx
+++ b/artfynd/A 44466-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1297747</v>
+        <v>485260</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hökensås - Kroksjön - Norr - Daretorp, Vg</t>
+          <t>KROKSJÖN, N om (1), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446414.7629612038</v>
+        <v>446347</v>
       </c>
       <c r="R2" t="n">
-        <v>6436896.426006332</v>
+        <v>6436888</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +741,19 @@
           <t>Daretorp</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>OV-Tid-3761</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-10-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1988-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>leg. Ewa Lilliesköld,Kurt-Anders Johansson,Rolf-Göran Carlsson. Tallskog och skogsväg norr om Kroksjön på Hökensås i Daretorp socken.</t>
+          <t>1988-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +764,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog och skogsväg norr om Kroksjön på Hökensås i Daretorp socken.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Enar Sahlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Ewa Grunditz Lilliesköld</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>VBSK fynddatabas</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -804,16 +787,11 @@
         <v>73695811</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446503.8630360234</v>
+        <v>446504</v>
       </c>
       <c r="R3" t="n">
-        <v>6436940.194116923</v>
+        <v>6436940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +852,9 @@
           <t>2018-05-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,56 +890,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>485260</v>
+        <v>112786053</v>
       </c>
       <c r="B4" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1853</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mosippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vernalis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>KROKSJÖN, N om (1), Vg</t>
+          <t>Hökensås, Kroksjöns östsida, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446346.8124677112</v>
+        <v>446503</v>
       </c>
       <c r="R4" t="n">
-        <v>6436888.347653459</v>
+        <v>6436913</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,29 +953,14 @@
           <t>Daretorp</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>OV-Tid-3761</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1988-06-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1988-06-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,39 +971,39 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Enar Sahlin</t>
+          <t>Emma Roland</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Emma Roland, Helena Bager</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112786053</v>
+        <v>112786054</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1086,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446504</v>
+        <v>446519</v>
       </c>
       <c r="R5" t="n">
-        <v>6436913</v>
+        <v>6436897</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1157,19 +1102,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112786058</v>
+        <v>112786055</v>
       </c>
       <c r="B6" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1197,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446567</v>
+        <v>446537</v>
       </c>
       <c r="R6" t="n">
-        <v>6436791</v>
+        <v>6436867</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1268,19 +1208,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112786054</v>
+        <v>112786057</v>
       </c>
       <c r="B7" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1308,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446520</v>
+        <v>446545</v>
       </c>
       <c r="R7" t="n">
-        <v>6436898</v>
+        <v>6436836</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1379,19 +1314,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112786055</v>
+        <v>112786058</v>
       </c>
       <c r="B8" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1419,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446537</v>
+        <v>446567</v>
       </c>
       <c r="R8" t="n">
-        <v>6436867</v>
+        <v>6436791</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1483,117 +1413,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>Sandbarrskog Västra Götaland</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112786057</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91162</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Hökensås, Kroksjöns östsida, Vg</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>446545</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6436836</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tidaholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Daretorp</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Emma Roland</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Emma Roland, Helena Bager</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>Sandbarrskog Västra Götaland</t>
         </is>

--- a/artfynd/A 44466-2023 artfynd.xlsx
+++ b/artfynd/A 44466-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -781,6 +786,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/485260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>Sandbarrsvampar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73695811</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112786053</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112786054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112786055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112786057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,8 +1452,22 @@
           <t>Sandbarrskog Västra Götaland</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112786058</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>